--- a/dataset/01.w_Defects/lock_never_unlock.xlsx
+++ b/dataset/01.w_Defects/lock_never_unlock.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pthread_mutex_t lock_never_unlock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_001_glb_data = 0; pthread_mutex_t lock_never_unlock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_002_glb_data = 0; pthread_mutex_t lock_never_unlock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float lock_never_unlock_003_glb_data = 1000.0; pthread_mutex_t lock_never_unlock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_005_glb_data = 0; int thread_set = 1; pthread_mutex_t lock_never_unlock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_007_glb_var = 0; pthread_mutex_t lock_never_unlock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; lock_never_unlock_008_s_001 lock_never_unlock_008_glb_sptr ={0}; pthread_mutex_t lock_never_unlock_009_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_009_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_009_glb_var = 0; extern volatile int vflag; void lock_never_unlock_004 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; pthread_create(&amp;th1, NULL, lock_never_unlock_004_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, lock_never_unlock_004_tsk_002, (void *)t2); sleep(1); #endif /* defined(CHECKER_POLYSPACE) */ } void *lock_never_unlock_004_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; pthread_mutex_lock( &amp;lock_never_unlock_004_glb_mutex_1 ); ip = (long)input; ip = ip *10; #if defined PRINT_DEBUG printf("Task4_1! Lock Never Unlock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ if (ip &lt; 0) pthread_mutex_unlock( &amp;lock_never_unlock_004_glb_mutex_1 );/*Tool should detect this line as error*/ /* ERROR:Lock Never Unlock */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * lock_never_unlock_004_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; pthread_mutex_lock( &amp;lock_never_unlock_004_glb_mutex_2 ); ip = (long)input; ip = ip *20; #if defined PRINT_DEBUG printf("Task4_2! Lock Never Unlock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ pthread_mutex_unlock( &amp;lock_never_unlock_004_glb_mutex_2 ); #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t lock_never_unlock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_001_glb_data = 0; pthread_mutex_t lock_never_unlock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_002_glb_data = 0; pthread_mutex_t lock_never_unlock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float lock_never_unlock_003_glb_data = 1000.0; pthread_mutex_t lock_never_unlock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_005_glb_data = 0; int thread_set = 1; pthread_mutex_t lock_never_unlock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_007_glb_var = 0; pthread_mutex_t lock_never_unlock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; lock_never_unlock_008_s_001 lock_never_unlock_008_glb_sptr ={0}; pthread_mutex_t lock_never_unlock_009_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_009_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_009_glb_var = 0; extern volatile int vflag; void lock_never_unlock_004 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; pthread_create(&amp;th1, NULL, lock_never_unlock_004_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, lock_never_unlock_004_tsk_002, (void *)t2); sleep(1); #endif /* defined(CHECKER_POLYSPACE) */ } void * lock_never_unlock_004_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; pthread_mutex_lock( &amp;lock_never_unlock_004_glb_mutex_2 ); ip = (long)input; ip = ip *20; #if defined PRINT_DEBUG printf("Task4_2! Lock Never Unlock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ pthread_mutex_unlock( &amp;lock_never_unlock_004_glb_mutex_2 ); #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *lock_never_unlock_004_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; pthread_mutex_lock( &amp;lock_never_unlock_004_glb_mutex_1 ); ip = (long)input; ip = ip *10; #if defined PRINT_DEBUG printf("Task4_1! Lock Never Unlock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ if (ip &lt; 0) pthread_mutex_unlock( &amp;lock_never_unlock_004_glb_mutex_1 );/*Tool should detect this line as error*/ /* ERROR:Lock Never Unlock */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pthread_mutex_t lock_never_unlock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_001_glb_data = 0; pthread_mutex_t lock_never_unlock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_002_glb_data = 0; pthread_mutex_t lock_never_unlock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float lock_never_unlock_003_glb_data = 1000.0; pthread_mutex_t lock_never_unlock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_005_glb_data = 0; int thread_set = 1; pthread_mutex_t lock_never_unlock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_007_glb_var = 0; pthread_mutex_t lock_never_unlock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; lock_never_unlock_008_s_001 lock_never_unlock_008_glb_sptr ={0}; pthread_mutex_t lock_never_unlock_009_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_009_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_009_glb_var = 0; extern volatile int vflag; void lock_never_unlock_008 () { int thread_set = 0; #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; if ( thread_set == CREATE_THREAD) { ; } else { pthread_create(&amp;th1, NULL, lock_never_unlock_008_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, lock_never_unlock_008_tsk_002, (void *)t2); sleep(1); } #endif /* defined(CHECKER_POLYSPACE) */ } void * lock_never_unlock_008_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i; ip = (long)input; ip = ip *20; for (i=0;i&lt;=4;i++) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;lock_never_unlock_008_glb_mutex_2 ); lock_never_unlock_008_glb_sptr.a += 20; pthread_mutex_unlock( &amp;lock_never_unlock_008_glb_mutex_2 ); } } #if defined PRINT_DEBUG printf("Task8_2! Lock But Never Unlock, thread #%ld! aa=%d\n",ip,lock_never_unlock_008_glb_sptr.a); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * lock_never_unlock_008_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i; ip = (long)input; ip = ip *10; for (i=0;i&lt;=4;i++) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;lock_never_unlock_008_glb_mutex_1 ); lock_never_unlock_008_glb_sptr.a += 10; if(i!=4) pthread_mutex_unlock( &amp;lock_never_unlock_008_glb_mutex_1 );/*Tool should detect this line as error*/ /* ERROR:Lock Never Unlock */ } } #if defined PRINT_DEBUG printf("Task8_1! Lock But Never Unlock, thread #%ld! aa=%d\n",ip,lock_never_unlock_008_glb_sptr.a); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t lock_never_unlock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_001_glb_data = 0; pthread_mutex_t lock_never_unlock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_002_glb_data = 0; pthread_mutex_t lock_never_unlock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float lock_never_unlock_003_glb_data = 1000.0; pthread_mutex_t lock_never_unlock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_005_glb_data = 0; int thread_set = 1; pthread_mutex_t lock_never_unlock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_007_glb_var = 0; pthread_mutex_t lock_never_unlock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; lock_never_unlock_008_s_001 lock_never_unlock_008_glb_sptr ={0}; pthread_mutex_t lock_never_unlock_009_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_009_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_009_glb_var = 0; extern volatile int vflag; void lock_never_unlock_008 () { int thread_set = 0; #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; if ( thread_set == CREATE_THREAD) { ; } else { pthread_create(&amp;th1, NULL, lock_never_unlock_008_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, lock_never_unlock_008_tsk_002, (void *)t2); sleep(1); } #endif /* defined(CHECKER_POLYSPACE) */ } void * lock_never_unlock_008_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i; ip = (long)input; ip = ip *10; for (i=0;i&lt;=4;i++) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;lock_never_unlock_008_glb_mutex_1 ); lock_never_unlock_008_glb_sptr.a += 10; if(i!=4) pthread_mutex_unlock( &amp;lock_never_unlock_008_glb_mutex_1 );/*Tool should detect this line as error*/ /* ERROR:Lock Never Unlock */ } } #if defined PRINT_DEBUG printf("Task8_1! Lock But Never Unlock, thread #%ld! aa=%d\n",ip,lock_never_unlock_008_glb_sptr.a); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * lock_never_unlock_008_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i; ip = (long)input; ip = ip *20; for (i=0;i&lt;=4;i++) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;lock_never_unlock_008_glb_mutex_2 ); lock_never_unlock_008_glb_sptr.a += 20; pthread_mutex_unlock( &amp;lock_never_unlock_008_glb_mutex_2 ); } } #if defined PRINT_DEBUG printf("Task8_2! Lock But Never Unlock, thread #%ld! aa=%d\n",ip,lock_never_unlock_008_glb_sptr.a); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pthread_mutex_t lock_never_unlock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_001_glb_data = 0; pthread_mutex_t lock_never_unlock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_002_glb_data = 0; pthread_mutex_t lock_never_unlock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float lock_never_unlock_003_glb_data = 1000.0; pthread_mutex_t lock_never_unlock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_005_glb_data = 0; int thread_set = 1; pthread_mutex_t lock_never_unlock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_007_glb_var = 0; pthread_mutex_t lock_never_unlock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; lock_never_unlock_008_s_001 lock_never_unlock_008_glb_sptr ={0}; pthread_mutex_t lock_never_unlock_009_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_009_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_009_glb_var = 0; extern volatile int vflag; void lock_never_unlock_009 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; pthread_create(&amp;th1, NULL, lock_never_unlock_009_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, lock_never_unlock_009_tsk_002, (void *)t2); pthread_join(th1, NULL); pthread_join(th2, NULL); #endif /* defined(CHECKER_POLYSPACE) */ } void *lock_never_unlock_009_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;lock_never_unlock_009_glb_mutex_1 ); lock_never_unlock_009_glb_var += 10; pthread_mutex_unlock( &amp;lock_never_unlock_009_glb_mutex_1 ); } i--; }while (i&gt;0); #if defined PRINT_DEBUG printf("Task7_1! Lock Never Unlock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * lock_never_unlock_009_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;lock_never_unlock_009_glb_mutex_2 ); if(i!=5) { lock_never_unlock_009_glb_var += 20; pthread_mutex_unlock( &amp;lock_never_unlock_009_glb_mutex_2 );/*Tool should detect this line as error*/ /* ERROR:Lock Never Unlock */ } } i--; } while (i&gt;0); #if defined PRINT_DEBUG printf("Task7_2! Lock Never Unlock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t lock_never_unlock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_001_glb_data = 0; pthread_mutex_t lock_never_unlock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_002_glb_data = 0; pthread_mutex_t lock_never_unlock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float lock_never_unlock_003_glb_data = 1000.0; pthread_mutex_t lock_never_unlock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_005_glb_data = 0; int thread_set = 1; pthread_mutex_t lock_never_unlock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_007_glb_var = 0; pthread_mutex_t lock_never_unlock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; lock_never_unlock_008_s_001 lock_never_unlock_008_glb_sptr ={0}; pthread_mutex_t lock_never_unlock_009_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t lock_never_unlock_009_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_009_glb_var = 0; extern volatile int vflag; void lock_never_unlock_009 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; long int t1 = 10; long int t2 = 20; pthread_create(&amp;th1, NULL, lock_never_unlock_009_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, lock_never_unlock_009_tsk_002, (void *)t2); pthread_join(th1, NULL); pthread_join(th2, NULL); #endif /* defined(CHECKER_POLYSPACE) */ } void * lock_never_unlock_009_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;lock_never_unlock_009_glb_mutex_2 ); if(i!=5) { lock_never_unlock_009_glb_var += 20; pthread_mutex_unlock( &amp;lock_never_unlock_009_glb_mutex_2 );/*Tool should detect this line as error*/ /* ERROR:Lock Never Unlock */ } } i--; } while (i&gt;0); #if defined PRINT_DEBUG printf("Task7_2! Lock Never Unlock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *lock_never_unlock_009_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;lock_never_unlock_009_glb_mutex_1 ); lock_never_unlock_009_glb_var += 10; pthread_mutex_unlock( &amp;lock_never_unlock_009_glb_mutex_1 ); } i--; }while (i&gt;0); #if defined PRINT_DEBUG printf("Task7_1! Lock Never Unlock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
